--- a/r5-core-ballot_2026_03/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-ballot_2026_03/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T09:39:47+00:00</t>
+    <t>2026-10-28T07:26:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-ballot_2026_03/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-ballot_2026_03/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T07:26:46+00:00</t>
+    <t>2026-10-28T07:37:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
